--- a/jpcore-r4/main/ValueSet-jp-observation-radiology-code-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-observation-radiology-code-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/ValueSet-jp-observation-radiology-code-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-observation-radiology-code-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/ValueSet-jp-observation-radiology-code-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-observation-radiology-code-vs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+    <t>Copyright JED-Project、JAHIS、日本医療情報学会FHIR国内実装基盤研究会  
 This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
